--- a/data/gravel/BMC URS AL 2025.xlsx
+++ b/data/gravel/BMC URS AL 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790EF818-9209-704D-B12C-06E37A30EBD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD09104-8C9F-6249-AFBB-BEB564EE6D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4040" yWindow="2640" windowWidth="24760" windowHeight="14180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>https://us.bmc-switzerland.com/cdn/shop/files/bmc-25ed-urs-al-one-gravel-bike-silver-1.jpg?v=1758292361&amp;width=1080</t>
   </si>
 </sst>
 </file>
@@ -759,6 +762,11 @@
         <v>114</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>118</v>
+      </c>
+    </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>

--- a/data/gravel/BMC URS AL 2025.xlsx
+++ b/data/gravel/BMC URS AL 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD09104-8C9F-6249-AFBB-BEB564EE6D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61711D95-FCFF-944C-AE81-CEE9295F10C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4040" yWindow="2640" windowWidth="24760" windowHeight="14180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="121">
   <si>
     <t>brand</t>
   </si>
@@ -377,6 +377,12 @@
   </si>
   <si>
     <t>https://us.bmc-switzerland.com/cdn/shop/files/bmc-25ed-urs-al-one-gravel-bike-silver-1.jpg?v=1758292361&amp;width=1080</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Grenchen, Switzerland</t>
   </si>
 </sst>
 </file>
@@ -716,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1730,6 +1736,14 @@
         <v>117</v>
       </c>
     </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>119</v>
+      </c>
+      <c r="B80" t="s">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/BMC URS AL 2025.xlsx
+++ b/data/gravel/BMC URS AL 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61711D95-FCFF-944C-AE81-CEE9295F10C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC5EE50-D3DA-A14D-8783-03DFEAA263EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4040" yWindow="2640" windowWidth="24760" windowHeight="14180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="121">
   <si>
     <t>brand</t>
   </si>
@@ -1646,6 +1646,9 @@
       <c r="A66" t="s">
         <v>94</v>
       </c>
+      <c r="B66" s="1" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">

--- a/data/gravel/BMC URS AL 2025.xlsx
+++ b/data/gravel/BMC URS AL 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC5EE50-D3DA-A14D-8783-03DFEAA263EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D71746B9-B9EB-C14C-B835-FFB7DD3234F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4040" yWindow="2640" windowWidth="24760" windowHeight="14180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="127">
   <si>
     <t>brand</t>
   </si>
@@ -383,6 +383,24 @@
   </si>
   <si>
     <t>Grenchen, Switzerland</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -722,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1588,162 +1606,192 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>86</v>
-      </c>
-      <c r="B58">
-        <v>27.2</v>
+        <v>123</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>92</v>
+        <v>86</v>
+      </c>
+      <c r="B64">
+        <v>27.2</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>93</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>94</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>97</v>
-      </c>
-      <c r="B69">
-        <v>2</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>99</v>
-      </c>
-      <c r="B71">
-        <v>1</v>
+        <v>93</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>100</v>
-      </c>
-      <c r="B72">
-        <v>3</v>
+        <v>94</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>101</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>102</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>103</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>115</v>
+        <v>97</v>
+      </c>
+      <c r="B75">
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B77">
-        <v>2499</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>106</v>
+        <v>100</v>
+      </c>
+      <c r="B78">
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>102</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>103</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>105</v>
+      </c>
+      <c r="B83">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>107</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>119</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B86" t="s">
         <v>120</v>
       </c>
     </row>
